--- a/public/fichas/formato_ficha_catastral.xlsx
+++ b/public/fichas/formato_ficha_catastral.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Josee\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sistema_catastro_definitivo\public\fichas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4CD60C-DB82-46CC-BC8F-88BDD154A64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17A986B-FF5A-4E74-90B0-71B5A1B82028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$AF$53</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>Republica Bolivariana de Venezuela</t>
   </si>
@@ -204,12 +207,6 @@
     </r>
   </si>
   <si>
-    <t>calle bolivar</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>Documento de Identidad N°:</t>
   </si>
 </sst>
@@ -221,7 +218,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="165" formatCode="[$-200A]d&quot; de &quot;mmmm&quot; de &quot;yyyy;@"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="37">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -289,14 +286,6 @@
       <color rgb="FF000000"/>
       <name val="Georgia Ref"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Georgia Ref"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -370,15 +359,6 @@
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <u/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Batik Regular"/>
       <family val="2"/>
     </font>
     <font>
@@ -488,6 +468,15 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -497,7 +486,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -705,75 +694,72 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
@@ -784,39 +770,66 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="justify"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -825,76 +838,79 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="justify"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -912,21 +928,21 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="37" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="35" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -934,20 +950,15 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -971,7 +982,7 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:colOff>107950</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>16949</xdr:rowOff>
     </xdr:from>
@@ -1008,8 +1019,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="222250" y="378899"/>
-          <a:ext cx="1428750" cy="990739"/>
+          <a:off x="177800" y="378899"/>
+          <a:ext cx="1473200" cy="990739"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1352,203 +1363,203 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
       <c r="AG1" s="4"/>
       <c r="AH1" s="4"/>
       <c r="AI1" s="4"/>
       <c r="AJ1" s="4"/>
     </row>
     <row r="2" spans="1:36" ht="14.5" thickBot="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
       <c r="AG2" s="4"/>
       <c r="AH2" s="4"/>
       <c r="AI2" s="4"/>
       <c r="AJ2" s="4"/>
     </row>
     <row r="3" spans="1:36" ht="16.5" thickBot="1">
-      <c r="F3" s="77" t="s">
+      <c r="F3" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="78"/>
-      <c r="U3" s="78"/>
-      <c r="V3" s="78"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="78"/>
-      <c r="Y3" s="78"/>
-      <c r="Z3" s="78"/>
-      <c r="AA3" s="78"/>
-      <c r="AB3" s="78"/>
-      <c r="AC3" s="78"/>
-      <c r="AD3" s="78"/>
-      <c r="AE3" s="78"/>
-      <c r="AF3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="79"/>
+      <c r="W3" s="79"/>
+      <c r="X3" s="79"/>
+      <c r="Y3" s="79"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
+      <c r="AB3" s="79"/>
+      <c r="AC3" s="79"/>
+      <c r="AD3" s="79"/>
+      <c r="AE3" s="79"/>
+      <c r="AF3" s="80"/>
       <c r="AG3" s="4"/>
       <c r="AH3" s="4"/>
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
     </row>
     <row r="4" spans="1:36" ht="14.5">
-      <c r="F4" s="80" t="s">
+      <c r="F4" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="81"/>
-      <c r="H4" s="82" t="s">
+      <c r="G4" s="82"/>
+      <c r="H4" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="83"/>
-      <c r="J4" s="82" t="s">
+      <c r="I4" s="84"/>
+      <c r="J4" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="83"/>
-      <c r="L4" s="82" t="s">
+      <c r="K4" s="84"/>
+      <c r="L4" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="84"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="82" t="s">
+      <c r="M4" s="85"/>
+      <c r="N4" s="84"/>
+      <c r="O4" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="84"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="82" t="s">
+      <c r="P4" s="85"/>
+      <c r="Q4" s="84"/>
+      <c r="R4" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="S4" s="84"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="82" t="s">
+      <c r="S4" s="85"/>
+      <c r="T4" s="84"/>
+      <c r="U4" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="V4" s="84"/>
-      <c r="W4" s="83"/>
-      <c r="X4" s="82" t="s">
+      <c r="V4" s="85"/>
+      <c r="W4" s="84"/>
+      <c r="X4" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="Y4" s="84"/>
-      <c r="Z4" s="83"/>
-      <c r="AA4" s="82" t="s">
+      <c r="Y4" s="85"/>
+      <c r="Z4" s="84"/>
+      <c r="AA4" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="AB4" s="84"/>
-      <c r="AC4" s="83"/>
-      <c r="AD4" s="82" t="s">
+      <c r="AB4" s="85"/>
+      <c r="AC4" s="84"/>
+      <c r="AD4" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="AE4" s="84"/>
-      <c r="AF4" s="83"/>
+      <c r="AE4" s="85"/>
+      <c r="AF4" s="84"/>
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
       <c r="AI4" s="4"/>
       <c r="AJ4" s="4"/>
     </row>
     <row r="5" spans="1:36" ht="15" thickBot="1">
-      <c r="F5" s="5">
+      <c r="F5" s="42">
         <v>0</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="43">
         <v>5</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="42">
         <v>0</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="44">
         <v>7</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="42">
         <v>0</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="45">
         <v>1</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="46">
         <v>0</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="43">
         <v>1</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="47">
         <v>0</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5" s="48">
         <v>0</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q5" s="94">
         <v>0</v>
       </c>
-      <c r="R5" s="10">
+      <c r="R5" s="47">
         <v>0</v>
       </c>
-      <c r="S5" s="11">
+      <c r="S5" s="48">
         <v>0</v>
       </c>
-      <c r="T5" s="8">
+      <c r="T5" s="45">
         <v>0</v>
       </c>
-      <c r="U5" s="10">
+      <c r="U5" s="47">
         <v>0</v>
       </c>
-      <c r="V5" s="11">
+      <c r="V5" s="48">
         <v>0</v>
       </c>
-      <c r="W5" s="8">
+      <c r="W5" s="45">
         <v>0</v>
       </c>
-      <c r="X5" s="10">
+      <c r="X5" s="47">
         <v>0</v>
       </c>
-      <c r="Y5" s="11">
+      <c r="Y5" s="48">
         <v>0</v>
       </c>
-      <c r="Z5" s="8">
+      <c r="Z5" s="45">
         <v>0</v>
       </c>
-      <c r="AA5" s="10">
+      <c r="AA5" s="47">
         <v>0</v>
       </c>
-      <c r="AB5" s="11">
+      <c r="AB5" s="48">
         <v>0</v>
       </c>
-      <c r="AC5" s="8">
+      <c r="AC5" s="45">
         <v>0</v>
       </c>
-      <c r="AD5" s="10">
+      <c r="AD5" s="47">
         <v>0</v>
       </c>
-      <c r="AE5" s="11">
+      <c r="AE5" s="48">
         <v>0</v>
       </c>
-      <c r="AF5" s="8">
+      <c r="AF5" s="45">
         <v>0</v>
       </c>
       <c r="AG5" s="4"/>
@@ -1557,93 +1568,93 @@
       <c r="AJ5" s="4"/>
     </row>
     <row r="6" spans="1:36" ht="14.5">
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="12"/>
-      <c r="AE6" s="12"/>
-      <c r="AF6" s="12"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="5"/>
       <c r="AG6" s="4"/>
       <c r="AH6" s="4"/>
       <c r="AI6" s="4"/>
       <c r="AJ6" s="4"/>
     </row>
     <row r="7" spans="1:36" ht="15.5">
-      <c r="N7" s="14" t="s">
+      <c r="N7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="85"/>
-      <c r="T7" s="85"/>
-      <c r="U7" s="85"/>
-      <c r="V7" s="85"/>
-      <c r="W7" s="85"/>
-      <c r="X7" s="85"/>
-      <c r="Y7" s="85"/>
-      <c r="Z7" s="85"/>
-      <c r="AA7" s="85"/>
-      <c r="AB7" s="85"/>
-      <c r="AC7" s="85"/>
-      <c r="AD7" s="85"/>
-      <c r="AE7" s="85"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="86"/>
+      <c r="T7" s="86"/>
+      <c r="U7" s="86"/>
+      <c r="V7" s="86"/>
+      <c r="W7" s="86"/>
+      <c r="X7" s="86"/>
+      <c r="Y7" s="86"/>
+      <c r="Z7" s="86"/>
+      <c r="AA7" s="86"/>
+      <c r="AB7" s="86"/>
+      <c r="AC7" s="86"/>
+      <c r="AD7" s="86"/>
+      <c r="AE7" s="86"/>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>
       <c r="AI7" s="4"/>
       <c r="AJ7" s="4"/>
     </row>
     <row r="8" spans="1:36">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
       <c r="AI8" s="4"/>
       <c r="AJ8" s="4"/>
     </row>
     <row r="9" spans="1:36" ht="15.5">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="76"/>
-      <c r="C9" s="76"/>
-      <c r="D9" s="76"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
-      <c r="Z9" s="15"/>
-      <c r="AA9" s="15"/>
-      <c r="AB9" s="15"/>
-      <c r="AC9" s="15"/>
-      <c r="AD9" s="15"/>
-      <c r="AE9" s="16"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="8"/>
+      <c r="AB9" s="8"/>
+      <c r="AC9" s="8"/>
+      <c r="AD9" s="8"/>
+      <c r="AE9" s="9"/>
       <c r="AG9" s="4"/>
       <c r="AH9" s="4"/>
       <c r="AI9" s="4"/>
@@ -1656,52 +1667,52 @@
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="Z10" s="15"/>
-      <c r="AA10" s="15"/>
-      <c r="AB10" s="15"/>
-      <c r="AC10" s="15"/>
-      <c r="AD10" s="15"/>
-      <c r="AE10" s="16"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="9"/>
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
       <c r="AI10" s="4"/>
       <c r="AJ10" s="4"/>
     </row>
     <row r="11" spans="1:36" ht="20">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="66"/>
-      <c r="K11" s="66"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="66"/>
-      <c r="N11" s="66"/>
-      <c r="O11" s="66"/>
-      <c r="P11" s="66"/>
-      <c r="Q11" s="66"/>
-      <c r="R11" s="66"/>
-      <c r="S11" s="66"/>
-      <c r="T11" s="66"/>
-      <c r="U11" s="66"/>
-      <c r="V11" s="66"/>
-      <c r="W11" s="66"/>
-      <c r="X11" s="66"/>
-      <c r="Y11" s="66"/>
-      <c r="Z11" s="66"/>
-      <c r="AA11" s="66"/>
-      <c r="AB11" s="66"/>
-      <c r="AC11" s="66"/>
-      <c r="AD11" s="66"/>
-      <c r="AE11" s="66"/>
-      <c r="AF11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="67"/>
+      <c r="N11" s="67"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="67"/>
+      <c r="Q11" s="67"/>
+      <c r="R11" s="67"/>
+      <c r="S11" s="67"/>
+      <c r="T11" s="67"/>
+      <c r="U11" s="67"/>
+      <c r="V11" s="67"/>
+      <c r="W11" s="67"/>
+      <c r="X11" s="67"/>
+      <c r="Y11" s="67"/>
+      <c r="Z11" s="67"/>
+      <c r="AA11" s="67"/>
+      <c r="AB11" s="67"/>
+      <c r="AC11" s="67"/>
+      <c r="AD11" s="67"/>
+      <c r="AE11" s="67"/>
+      <c r="AF11" s="67"/>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
       <c r="AI11" s="4"/>
@@ -1710,73 +1721,73 @@
     <row r="12" spans="1:36">
       <c r="AG12" s="49"/>
       <c r="AH12" s="49"/>
-      <c r="AI12" s="17"/>
-      <c r="AJ12" s="17"/>
+      <c r="AI12" s="10"/>
+      <c r="AJ12" s="10"/>
     </row>
     <row r="13" spans="1:36" ht="15.5">
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="12"/>
+      <c r="D13" s="5"/>
       <c r="AG13" s="4"/>
       <c r="AH13" s="4"/>
       <c r="AI13" s="4"/>
       <c r="AJ13" s="4"/>
     </row>
     <row r="14" spans="1:36" ht="14.25" customHeight="1">
-      <c r="A14" s="69" t="s">
+      <c r="A14" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="69"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="69"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="75"/>
-      <c r="O14" s="75"/>
-      <c r="P14" s="75"/>
-      <c r="Q14" s="75"/>
-      <c r="R14" s="75"/>
-      <c r="S14" s="75"/>
-      <c r="T14" s="75"/>
-      <c r="U14" s="75"/>
-      <c r="V14" s="75"/>
-      <c r="W14" s="75"/>
-      <c r="X14" s="75"/>
-      <c r="Y14" s="75"/>
-      <c r="Z14" s="75"/>
-      <c r="AA14" s="75"/>
-      <c r="AB14" s="75"/>
-      <c r="AC14" s="75"/>
-      <c r="AD14" s="75"/>
-      <c r="AE14" s="75"/>
-      <c r="AF14" s="75"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="70"/>
+      <c r="M14" s="70"/>
+      <c r="N14" s="76"/>
+      <c r="O14" s="76"/>
+      <c r="P14" s="76"/>
+      <c r="Q14" s="76"/>
+      <c r="R14" s="76"/>
+      <c r="S14" s="76"/>
+      <c r="T14" s="76"/>
+      <c r="U14" s="76"/>
+      <c r="V14" s="76"/>
+      <c r="W14" s="76"/>
+      <c r="X14" s="76"/>
+      <c r="Y14" s="76"/>
+      <c r="Z14" s="76"/>
+      <c r="AA14" s="76"/>
+      <c r="AB14" s="76"/>
+      <c r="AC14" s="76"/>
+      <c r="AD14" s="76"/>
+      <c r="AE14" s="76"/>
+      <c r="AF14" s="76"/>
       <c r="AG14" s="4"/>
       <c r="AH14" s="4"/>
       <c r="AI14" s="4"/>
       <c r="AJ14" s="4"/>
     </row>
     <row r="15" spans="1:36" ht="15" customHeight="1">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="74"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
       <c r="N15" s="52"/>
       <c r="O15" s="52"/>
       <c r="P15" s="52"/>
@@ -1802,218 +1813,212 @@
       <c r="AJ15" s="4"/>
     </row>
     <row r="16" spans="1:36" ht="16">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="70" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="67"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="71"/>
-      <c r="T16" s="71"/>
-      <c r="U16" s="71"/>
-      <c r="V16" s="71"/>
-      <c r="W16" s="71"/>
-      <c r="X16" s="71"/>
-      <c r="Y16" s="71"/>
-      <c r="Z16" s="72"/>
-      <c r="AA16" s="72"/>
-      <c r="AB16" s="72"/>
-      <c r="AC16" s="72"/>
-      <c r="AD16" s="72"/>
-      <c r="AE16" s="72"/>
-      <c r="AF16" s="21"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="72"/>
+      <c r="V16" s="72"/>
+      <c r="W16" s="72"/>
+      <c r="X16" s="72"/>
+      <c r="Y16" s="72"/>
+      <c r="Z16" s="73"/>
+      <c r="AA16" s="73"/>
+      <c r="AB16" s="73"/>
+      <c r="AC16" s="73"/>
+      <c r="AD16" s="73"/>
+      <c r="AE16" s="73"/>
+      <c r="AF16" s="13"/>
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
       <c r="AI16" s="4"/>
       <c r="AJ16" s="4"/>
     </row>
     <row r="17" spans="1:36" ht="12.75" customHeight="1">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="12"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="5"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
       <c r="AI17" s="4"/>
       <c r="AJ17" s="4"/>
     </row>
     <row r="18" spans="1:36" ht="15.5">
-      <c r="C18" s="65" t="s">
+      <c r="C18" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
-      <c r="V18" s="23"/>
-      <c r="W18" s="23"/>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="23"/>
-      <c r="AA18" s="23"/>
-      <c r="AB18" s="23"/>
-      <c r="AC18" s="23"/>
-      <c r="AD18" s="23"/>
-      <c r="AE18" s="23"/>
-      <c r="AF18" s="23"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="15"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="15"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="15"/>
+      <c r="Y18" s="15"/>
+      <c r="Z18" s="15"/>
+      <c r="AA18" s="15"/>
+      <c r="AB18" s="15"/>
+      <c r="AC18" s="15"/>
+      <c r="AD18" s="15"/>
+      <c r="AE18" s="15"/>
+      <c r="AF18" s="15"/>
       <c r="AG18" s="4"/>
       <c r="AH18" s="4"/>
       <c r="AI18" s="4"/>
       <c r="AJ18" s="4"/>
     </row>
     <row r="19" spans="1:36">
-      <c r="C19" s="43" t="s">
+      <c r="C19" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="73"/>
-      <c r="K19" s="73"/>
-      <c r="L19" s="73"/>
-      <c r="M19" s="73"/>
-      <c r="N19" s="73"/>
-      <c r="O19" s="73"/>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="73"/>
-      <c r="R19" s="73"/>
-      <c r="S19" s="73"/>
-      <c r="T19" s="73"/>
-      <c r="U19" s="73"/>
-      <c r="V19" s="73"/>
-      <c r="W19" s="73"/>
-      <c r="X19" s="73"/>
-      <c r="Y19" s="73"/>
-      <c r="Z19" s="73"/>
-      <c r="AA19" s="73"/>
-      <c r="AB19" s="73"/>
-      <c r="AC19" s="73"/>
-      <c r="AD19" s="73"/>
-      <c r="AE19" s="73"/>
-      <c r="AF19" s="24"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="74"/>
+      <c r="K19" s="74"/>
+      <c r="L19" s="74"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="74"/>
+      <c r="P19" s="74"/>
+      <c r="Q19" s="74"/>
+      <c r="R19" s="74"/>
+      <c r="S19" s="74"/>
+      <c r="T19" s="74"/>
+      <c r="U19" s="74"/>
+      <c r="V19" s="74"/>
+      <c r="W19" s="74"/>
+      <c r="X19" s="74"/>
+      <c r="Y19" s="74"/>
+      <c r="Z19" s="74"/>
+      <c r="AA19" s="74"/>
+      <c r="AB19" s="74"/>
+      <c r="AC19" s="74"/>
+      <c r="AD19" s="74"/>
+      <c r="AE19" s="74"/>
+      <c r="AF19" s="16"/>
       <c r="AG19" s="4"/>
       <c r="AH19" s="4"/>
       <c r="AI19" s="4"/>
       <c r="AJ19" s="4"/>
     </row>
     <row r="20" spans="1:36" ht="21" customHeight="1">
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="63" t="s">
+      <c r="D20" s="34"/>
+      <c r="E20" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="68" t="s">
-        <v>54</v>
-      </c>
-      <c r="L20" s="68"/>
-      <c r="M20" s="68"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="68"/>
-      <c r="P20" s="68"/>
-      <c r="Q20" s="68"/>
-      <c r="R20" s="68"/>
-      <c r="S20" s="68"/>
-      <c r="T20" s="68"/>
-      <c r="U20" s="68"/>
-      <c r="V20" s="68"/>
-      <c r="W20" s="68"/>
-      <c r="X20" s="68"/>
-      <c r="Y20" s="68"/>
-      <c r="Z20" s="68"/>
-      <c r="AA20" s="68"/>
-      <c r="AB20" s="68"/>
-      <c r="AC20" s="68"/>
-      <c r="AD20" s="68"/>
-      <c r="AE20" s="68"/>
-      <c r="AF20" s="68"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="69"/>
+      <c r="L20" s="69"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="69"/>
+      <c r="O20" s="69"/>
+      <c r="P20" s="69"/>
+      <c r="Q20" s="69"/>
+      <c r="R20" s="69"/>
+      <c r="S20" s="69"/>
+      <c r="T20" s="69"/>
+      <c r="U20" s="69"/>
+      <c r="V20" s="69"/>
+      <c r="W20" s="69"/>
+      <c r="X20" s="69"/>
+      <c r="Y20" s="69"/>
+      <c r="Z20" s="69"/>
+      <c r="AA20" s="69"/>
+      <c r="AB20" s="69"/>
+      <c r="AC20" s="69"/>
+      <c r="AD20" s="69"/>
+      <c r="AE20" s="69"/>
+      <c r="AF20" s="69"/>
       <c r="AG20" s="4"/>
       <c r="AH20" s="4"/>
       <c r="AI20" s="4"/>
       <c r="AJ20" s="4"/>
     </row>
     <row r="21" spans="1:36" ht="6.75" customHeight="1">
-      <c r="C21" s="25"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="26"/>
-      <c r="Q21" s="26"/>
-      <c r="R21" s="26"/>
-      <c r="S21" s="26"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="26"/>
-      <c r="V21" s="26"/>
-      <c r="W21" s="26"/>
-      <c r="X21" s="26"/>
-      <c r="Y21" s="26"/>
-      <c r="Z21" s="26"/>
-      <c r="AA21" s="26"/>
-      <c r="AB21" s="26"/>
-      <c r="AC21" s="26"/>
-      <c r="AD21" s="26"/>
-      <c r="AE21" s="26"/>
-      <c r="AF21" s="26"/>
+      <c r="C21" s="17"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="18"/>
+      <c r="AA21" s="18"/>
+      <c r="AB21" s="18"/>
+      <c r="AC21" s="18"/>
+      <c r="AD21" s="18"/>
+      <c r="AE21" s="18"/>
+      <c r="AF21" s="18"/>
       <c r="AG21" s="4"/>
       <c r="AH21" s="4"/>
       <c r="AI21" s="4"/>
       <c r="AJ21" s="4"/>
     </row>
     <row r="22" spans="1:36" ht="15.75" customHeight="1">
-      <c r="C22" s="25"/>
+      <c r="C22" s="17"/>
       <c r="G22" s="50" t="s">
         <v>25</v>
       </c>
@@ -2034,487 +2039,487 @@
       <c r="AJ22" s="4"/>
     </row>
     <row r="23" spans="1:36">
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
       <c r="G23" s="51"/>
       <c r="H23" s="51"/>
       <c r="I23" s="51"/>
       <c r="J23" s="51"/>
-      <c r="K23" s="46" t="s">
+      <c r="K23" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="L23" s="27"/>
-      <c r="M23" s="28"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="28"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="20"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="20"/>
       <c r="T23" s="51"/>
       <c r="U23" s="51"/>
       <c r="V23" s="51"/>
       <c r="W23" s="51"/>
-      <c r="X23" s="46" t="s">
+      <c r="X23" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="31"/>
-      <c r="AB23" s="31"/>
-      <c r="AC23" s="31"/>
-      <c r="AD23" s="31"/>
+      <c r="Y23" s="19"/>
+      <c r="Z23" s="23"/>
+      <c r="AA23" s="23"/>
+      <c r="AB23" s="23"/>
+      <c r="AC23" s="23"/>
+      <c r="AD23" s="23"/>
       <c r="AG23" s="4"/>
       <c r="AH23" s="4"/>
       <c r="AI23" s="4"/>
       <c r="AJ23" s="4"/>
     </row>
     <row r="24" spans="1:36">
-      <c r="C24" s="43" t="s">
+      <c r="C24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="51"/>
       <c r="H24" s="51"/>
       <c r="I24" s="51"/>
       <c r="J24" s="51"/>
-      <c r="K24" s="47" t="s">
+      <c r="K24" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="L24" s="27"/>
-      <c r="M24" s="28"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="28"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="20"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="20"/>
       <c r="T24" s="51"/>
       <c r="U24" s="51"/>
       <c r="V24" s="51"/>
       <c r="W24" s="51"/>
-      <c r="X24" s="47" t="s">
+      <c r="X24" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="Y24" s="27"/>
-      <c r="Z24" s="31"/>
-      <c r="AA24" s="31"/>
-      <c r="AB24" s="31"/>
-      <c r="AC24" s="31"/>
-      <c r="AD24" s="31"/>
+      <c r="Y24" s="19"/>
+      <c r="Z24" s="23"/>
+      <c r="AA24" s="23"/>
+      <c r="AB24" s="23"/>
+      <c r="AC24" s="23"/>
+      <c r="AD24" s="23"/>
       <c r="AG24" s="4"/>
       <c r="AH24" s="4"/>
       <c r="AI24" s="4"/>
       <c r="AJ24" s="4"/>
     </row>
     <row r="25" spans="1:36" ht="8.25" customHeight="1">
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="32"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="33"/>
-      <c r="T25" s="33"/>
-      <c r="U25" s="33"/>
-      <c r="V25" s="33"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="33"/>
-      <c r="Y25" s="34"/>
-      <c r="Z25" s="34"/>
-      <c r="AA25" s="34"/>
-      <c r="AB25" s="34"/>
-      <c r="AC25" s="34"/>
-      <c r="AD25" s="34"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="25"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="26"/>
+      <c r="Z25" s="26"/>
+      <c r="AA25" s="26"/>
+      <c r="AB25" s="26"/>
+      <c r="AC25" s="26"/>
+      <c r="AD25" s="26"/>
       <c r="AG25" s="4"/>
       <c r="AH25" s="4"/>
       <c r="AI25" s="4"/>
       <c r="AJ25" s="4"/>
     </row>
     <row r="26" spans="1:36" ht="15.5">
-      <c r="C26" s="48" t="s">
+      <c r="C26" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-      <c r="W26" s="27"/>
-      <c r="X26" s="27"/>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="27"/>
-      <c r="AA26" s="27"/>
-      <c r="AB26" s="27"/>
-      <c r="AC26" s="27"/>
-      <c r="AD26" s="27"/>
-      <c r="AE26" s="27"/>
-      <c r="AF26" s="27"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="19"/>
+      <c r="Y26" s="19"/>
+      <c r="Z26" s="19"/>
+      <c r="AA26" s="19"/>
+      <c r="AB26" s="19"/>
+      <c r="AC26" s="19"/>
+      <c r="AD26" s="19"/>
+      <c r="AE26" s="19"/>
+      <c r="AF26" s="19"/>
       <c r="AG26" s="4"/>
       <c r="AH26" s="4"/>
       <c r="AI26" s="4"/>
       <c r="AJ26" s="4"/>
     </row>
     <row r="27" spans="1:36" ht="15" customHeight="1">
-      <c r="C27" s="45" t="s">
+      <c r="C27" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="35"/>
-      <c r="E27" s="94"/>
-      <c r="F27" s="94"/>
-      <c r="G27" s="94"/>
-      <c r="H27" s="94"/>
-      <c r="I27" s="94"/>
-      <c r="J27" s="94"/>
-      <c r="K27" s="94"/>
-      <c r="L27" s="94"/>
-      <c r="M27" s="94"/>
-      <c r="N27" s="94"/>
-      <c r="O27" s="94"/>
-      <c r="P27" s="94"/>
-      <c r="Q27" s="94"/>
-      <c r="R27" s="94"/>
-      <c r="S27" s="94"/>
-      <c r="T27" s="94"/>
-      <c r="U27" s="94"/>
-      <c r="V27" s="94"/>
-      <c r="W27" s="94"/>
-      <c r="X27" s="94"/>
-      <c r="Y27" s="94"/>
-      <c r="Z27" s="94"/>
-      <c r="AA27" s="94"/>
-      <c r="AB27" s="94"/>
-      <c r="AC27" s="94"/>
-      <c r="AD27" s="94"/>
-      <c r="AE27" s="94"/>
-      <c r="AF27" s="94"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="62"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="62"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="62"/>
+      <c r="R27" s="62"/>
+      <c r="S27" s="62"/>
+      <c r="T27" s="62"/>
+      <c r="U27" s="62"/>
+      <c r="V27" s="62"/>
+      <c r="W27" s="62"/>
+      <c r="X27" s="62"/>
+      <c r="Y27" s="62"/>
+      <c r="Z27" s="62"/>
+      <c r="AA27" s="62"/>
+      <c r="AB27" s="62"/>
+      <c r="AC27" s="62"/>
+      <c r="AD27" s="62"/>
+      <c r="AE27" s="62"/>
+      <c r="AF27" s="62"/>
       <c r="AG27" s="4"/>
       <c r="AH27" s="4"/>
       <c r="AI27" s="4"/>
       <c r="AJ27" s="4"/>
     </row>
     <row r="28" spans="1:36" ht="11.25" customHeight="1">
-      <c r="C28" s="45"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="95"/>
-      <c r="F28" s="95"/>
-      <c r="G28" s="95"/>
-      <c r="H28" s="95"/>
-      <c r="I28" s="95"/>
-      <c r="J28" s="95"/>
-      <c r="K28" s="95"/>
-      <c r="L28" s="95"/>
-      <c r="M28" s="95"/>
-      <c r="N28" s="95"/>
-      <c r="O28" s="95"/>
-      <c r="P28" s="95"/>
-      <c r="Q28" s="95"/>
-      <c r="R28" s="95"/>
-      <c r="S28" s="95"/>
-      <c r="T28" s="95"/>
-      <c r="U28" s="95"/>
-      <c r="V28" s="95"/>
-      <c r="W28" s="95"/>
-      <c r="X28" s="95"/>
-      <c r="Y28" s="95"/>
-      <c r="Z28" s="95"/>
-      <c r="AA28" s="95"/>
-      <c r="AB28" s="95"/>
-      <c r="AC28" s="95"/>
-      <c r="AD28" s="95"/>
-      <c r="AE28" s="95"/>
-      <c r="AF28" s="95"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="41"/>
+      <c r="S28" s="41"/>
+      <c r="T28" s="41"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="41"/>
+      <c r="W28" s="41"/>
+      <c r="X28" s="41"/>
+      <c r="Y28" s="41"/>
+      <c r="Z28" s="41"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="41"/>
+      <c r="AC28" s="41"/>
+      <c r="AD28" s="41"/>
+      <c r="AE28" s="41"/>
+      <c r="AF28" s="41"/>
       <c r="AG28" s="4"/>
       <c r="AH28" s="4"/>
       <c r="AI28" s="4"/>
       <c r="AJ28" s="4"/>
     </row>
     <row r="29" spans="1:36" ht="15" customHeight="1">
-      <c r="C29" s="45" t="s">
+      <c r="C29" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="35"/>
-      <c r="E29" s="94"/>
-      <c r="F29" s="94"/>
-      <c r="G29" s="94"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="94"/>
-      <c r="J29" s="94"/>
-      <c r="K29" s="94"/>
-      <c r="L29" s="94"/>
-      <c r="M29" s="94"/>
-      <c r="N29" s="94"/>
-      <c r="O29" s="94"/>
-      <c r="P29" s="94"/>
-      <c r="Q29" s="94"/>
-      <c r="R29" s="94"/>
-      <c r="S29" s="94"/>
-      <c r="T29" s="94"/>
-      <c r="U29" s="94"/>
-      <c r="V29" s="94"/>
-      <c r="W29" s="94"/>
-      <c r="X29" s="94"/>
-      <c r="Y29" s="94"/>
-      <c r="Z29" s="94"/>
-      <c r="AA29" s="94"/>
-      <c r="AB29" s="94"/>
-      <c r="AC29" s="94"/>
-      <c r="AD29" s="94"/>
-      <c r="AE29" s="94"/>
-      <c r="AF29" s="94"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="62"/>
+      <c r="M29" s="62"/>
+      <c r="N29" s="62"/>
+      <c r="O29" s="62"/>
+      <c r="P29" s="62"/>
+      <c r="Q29" s="62"/>
+      <c r="R29" s="62"/>
+      <c r="S29" s="62"/>
+      <c r="T29" s="62"/>
+      <c r="U29" s="62"/>
+      <c r="V29" s="62"/>
+      <c r="W29" s="62"/>
+      <c r="X29" s="62"/>
+      <c r="Y29" s="62"/>
+      <c r="Z29" s="62"/>
+      <c r="AA29" s="62"/>
+      <c r="AB29" s="62"/>
+      <c r="AC29" s="62"/>
+      <c r="AD29" s="62"/>
+      <c r="AE29" s="62"/>
+      <c r="AF29" s="62"/>
       <c r="AG29" s="4"/>
       <c r="AH29" s="4"/>
       <c r="AI29" s="4"/>
       <c r="AJ29" s="4"/>
     </row>
     <row r="30" spans="1:36" ht="9.75" customHeight="1">
-      <c r="C30" s="45"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="95"/>
-      <c r="I30" s="95"/>
-      <c r="J30" s="95"/>
-      <c r="K30" s="95"/>
-      <c r="L30" s="95"/>
-      <c r="M30" s="95"/>
-      <c r="N30" s="95"/>
-      <c r="O30" s="95"/>
-      <c r="P30" s="95"/>
-      <c r="Q30" s="95"/>
-      <c r="R30" s="95"/>
-      <c r="S30" s="95"/>
-      <c r="T30" s="95"/>
-      <c r="U30" s="95"/>
-      <c r="V30" s="95"/>
-      <c r="W30" s="95"/>
-      <c r="X30" s="95"/>
-      <c r="Y30" s="95"/>
-      <c r="Z30" s="95"/>
-      <c r="AA30" s="95"/>
-      <c r="AB30" s="95"/>
-      <c r="AC30" s="95"/>
-      <c r="AD30" s="95"/>
-      <c r="AE30" s="95"/>
-      <c r="AF30" s="95"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="41"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="41"/>
+      <c r="Z30" s="41"/>
+      <c r="AA30" s="41"/>
+      <c r="AB30" s="41"/>
+      <c r="AC30" s="41"/>
+      <c r="AD30" s="41"/>
+      <c r="AE30" s="41"/>
+      <c r="AF30" s="41"/>
       <c r="AG30" s="4"/>
       <c r="AH30" s="4"/>
       <c r="AI30" s="4"/>
       <c r="AJ30" s="4"/>
     </row>
     <row r="31" spans="1:36" ht="15" customHeight="1">
-      <c r="C31" s="45" t="s">
+      <c r="C31" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="D31" s="35"/>
-      <c r="E31" s="94"/>
-      <c r="F31" s="94"/>
-      <c r="G31" s="94"/>
-      <c r="H31" s="94"/>
-      <c r="I31" s="94"/>
-      <c r="J31" s="94"/>
-      <c r="K31" s="94"/>
-      <c r="L31" s="94"/>
-      <c r="M31" s="94"/>
-      <c r="N31" s="94"/>
-      <c r="O31" s="94"/>
-      <c r="P31" s="94"/>
-      <c r="Q31" s="94"/>
-      <c r="R31" s="94"/>
-      <c r="S31" s="94"/>
-      <c r="T31" s="94"/>
-      <c r="U31" s="94"/>
-      <c r="V31" s="94"/>
-      <c r="W31" s="94"/>
-      <c r="X31" s="94"/>
-      <c r="Y31" s="94"/>
-      <c r="Z31" s="94"/>
-      <c r="AA31" s="94"/>
-      <c r="AB31" s="94"/>
-      <c r="AC31" s="94"/>
-      <c r="AD31" s="94"/>
-      <c r="AE31" s="94"/>
-      <c r="AF31" s="94"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="62"/>
+      <c r="J31" s="62"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="62"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="62"/>
+      <c r="O31" s="62"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="62"/>
+      <c r="R31" s="62"/>
+      <c r="S31" s="62"/>
+      <c r="T31" s="62"/>
+      <c r="U31" s="62"/>
+      <c r="V31" s="62"/>
+      <c r="W31" s="62"/>
+      <c r="X31" s="62"/>
+      <c r="Y31" s="62"/>
+      <c r="Z31" s="62"/>
+      <c r="AA31" s="62"/>
+      <c r="AB31" s="62"/>
+      <c r="AC31" s="62"/>
+      <c r="AD31" s="62"/>
+      <c r="AE31" s="62"/>
+      <c r="AF31" s="62"/>
       <c r="AG31" s="4"/>
       <c r="AH31" s="4"/>
       <c r="AI31" s="4"/>
       <c r="AJ31" s="4"/>
     </row>
     <row r="32" spans="1:36" ht="9" customHeight="1">
-      <c r="C32" s="45"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="95"/>
-      <c r="F32" s="95"/>
-      <c r="G32" s="95"/>
-      <c r="H32" s="95"/>
-      <c r="I32" s="95"/>
-      <c r="J32" s="95"/>
-      <c r="K32" s="95"/>
-      <c r="L32" s="95"/>
-      <c r="M32" s="95"/>
-      <c r="N32" s="95"/>
-      <c r="O32" s="95"/>
-      <c r="P32" s="95"/>
-      <c r="Q32" s="95"/>
-      <c r="R32" s="95"/>
-      <c r="S32" s="95"/>
-      <c r="T32" s="95"/>
-      <c r="U32" s="95"/>
-      <c r="V32" s="95"/>
-      <c r="W32" s="95"/>
-      <c r="X32" s="95"/>
-      <c r="Y32" s="95"/>
-      <c r="Z32" s="95"/>
-      <c r="AA32" s="95"/>
-      <c r="AB32" s="95"/>
-      <c r="AC32" s="95"/>
-      <c r="AD32" s="95"/>
-      <c r="AE32" s="95"/>
-      <c r="AF32" s="95"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="41"/>
+      <c r="M32" s="41"/>
+      <c r="N32" s="41"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="41"/>
+      <c r="S32" s="41"/>
+      <c r="T32" s="41"/>
+      <c r="U32" s="41"/>
+      <c r="V32" s="41"/>
+      <c r="W32" s="41"/>
+      <c r="X32" s="41"/>
+      <c r="Y32" s="41"/>
+      <c r="Z32" s="41"/>
+      <c r="AA32" s="41"/>
+      <c r="AB32" s="41"/>
+      <c r="AC32" s="41"/>
+      <c r="AD32" s="41"/>
+      <c r="AE32" s="41"/>
+      <c r="AF32" s="41"/>
       <c r="AG32" s="4"/>
       <c r="AH32" s="4"/>
       <c r="AI32" s="4"/>
       <c r="AJ32" s="4"/>
     </row>
     <row r="33" spans="1:36">
-      <c r="C33" s="45" t="s">
+      <c r="C33" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="35"/>
-      <c r="E33" s="94"/>
-      <c r="F33" s="94"/>
-      <c r="G33" s="94"/>
-      <c r="H33" s="94"/>
-      <c r="I33" s="94"/>
-      <c r="J33" s="94"/>
-      <c r="K33" s="94"/>
-      <c r="L33" s="94"/>
-      <c r="M33" s="94"/>
-      <c r="N33" s="94"/>
-      <c r="O33" s="94"/>
-      <c r="P33" s="94"/>
-      <c r="Q33" s="94"/>
-      <c r="R33" s="94"/>
-      <c r="S33" s="94"/>
-      <c r="T33" s="94"/>
-      <c r="U33" s="94"/>
-      <c r="V33" s="94"/>
-      <c r="W33" s="94"/>
-      <c r="X33" s="94"/>
-      <c r="Y33" s="94"/>
-      <c r="Z33" s="94"/>
-      <c r="AA33" s="94"/>
-      <c r="AB33" s="94"/>
-      <c r="AC33" s="94"/>
-      <c r="AD33" s="94"/>
-      <c r="AE33" s="94"/>
-      <c r="AF33" s="94"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="62"/>
+      <c r="J33" s="62"/>
+      <c r="K33" s="62"/>
+      <c r="L33" s="62"/>
+      <c r="M33" s="62"/>
+      <c r="N33" s="62"/>
+      <c r="O33" s="62"/>
+      <c r="P33" s="62"/>
+      <c r="Q33" s="62"/>
+      <c r="R33" s="62"/>
+      <c r="S33" s="62"/>
+      <c r="T33" s="62"/>
+      <c r="U33" s="62"/>
+      <c r="V33" s="62"/>
+      <c r="W33" s="62"/>
+      <c r="X33" s="62"/>
+      <c r="Y33" s="62"/>
+      <c r="Z33" s="62"/>
+      <c r="AA33" s="62"/>
+      <c r="AB33" s="62"/>
+      <c r="AC33" s="62"/>
+      <c r="AD33" s="62"/>
+      <c r="AE33" s="62"/>
+      <c r="AF33" s="62"/>
       <c r="AG33" s="4"/>
       <c r="AH33" s="4"/>
       <c r="AI33" s="4"/>
       <c r="AJ33" s="4"/>
     </row>
     <row r="34" spans="1:36" ht="9.75" customHeight="1">
-      <c r="C34" s="36"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="37"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="37"/>
-      <c r="N34" s="37"/>
-      <c r="O34" s="37"/>
-      <c r="P34" s="37"/>
-      <c r="Q34" s="37"/>
-      <c r="R34" s="37"/>
-      <c r="S34" s="37"/>
-      <c r="T34" s="37"/>
-      <c r="U34" s="37"/>
-      <c r="V34" s="37"/>
-      <c r="W34" s="37"/>
-      <c r="X34" s="37"/>
-      <c r="Y34" s="37"/>
-      <c r="Z34" s="37"/>
-      <c r="AA34" s="37"/>
-      <c r="AB34" s="37"/>
-      <c r="AC34" s="37"/>
-      <c r="AD34" s="37"/>
-      <c r="AE34" s="37"/>
-      <c r="AF34" s="37"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="29"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="29"/>
+      <c r="S34" s="29"/>
+      <c r="T34" s="29"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="29"/>
+      <c r="W34" s="29"/>
+      <c r="X34" s="29"/>
+      <c r="Y34" s="29"/>
+      <c r="Z34" s="29"/>
+      <c r="AA34" s="29"/>
+      <c r="AB34" s="29"/>
+      <c r="AC34" s="29"/>
+      <c r="AD34" s="29"/>
+      <c r="AE34" s="29"/>
+      <c r="AF34" s="29"/>
       <c r="AG34" s="4"/>
       <c r="AH34" s="4"/>
       <c r="AI34" s="4"/>
       <c r="AJ34" s="4"/>
     </row>
     <row r="35" spans="1:36" ht="15.5">
-      <c r="C35" s="65" t="s">
+      <c r="C35" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="27"/>
-      <c r="P35" s="27"/>
-      <c r="Q35" s="27"/>
-      <c r="R35" s="27"/>
-      <c r="S35" s="27"/>
-      <c r="T35" s="27"/>
-      <c r="U35" s="27"/>
-      <c r="V35" s="27"/>
-      <c r="W35" s="27"/>
-      <c r="X35" s="27"/>
-      <c r="Y35" s="27"/>
-      <c r="Z35" s="27"/>
-      <c r="AA35" s="27"/>
-      <c r="AB35" s="27"/>
-      <c r="AC35" s="27"/>
-      <c r="AD35" s="27"/>
-      <c r="AE35" s="27"/>
-      <c r="AF35" s="27"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="19"/>
+      <c r="Q35" s="19"/>
+      <c r="R35" s="19"/>
+      <c r="S35" s="19"/>
+      <c r="T35" s="19"/>
+      <c r="U35" s="19"/>
+      <c r="V35" s="19"/>
+      <c r="W35" s="19"/>
+      <c r="X35" s="19"/>
+      <c r="Y35" s="19"/>
+      <c r="Z35" s="19"/>
+      <c r="AA35" s="19"/>
+      <c r="AB35" s="19"/>
+      <c r="AC35" s="19"/>
+      <c r="AD35" s="19"/>
+      <c r="AE35" s="19"/>
+      <c r="AF35" s="19"/>
       <c r="AG35" s="4"/>
       <c r="AH35" s="4"/>
       <c r="AI35" s="4"/>
       <c r="AJ35" s="4"/>
     </row>
     <row r="36" spans="1:36" ht="42" customHeight="1">
-      <c r="B36" s="23"/>
+      <c r="B36" s="15"/>
       <c r="C36" s="60" t="s">
         <v>36</v>
       </c>
@@ -2553,222 +2558,222 @@
       <c r="AJ36" s="4"/>
     </row>
     <row r="37" spans="1:36">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="43" t="s">
+      <c r="B37" s="19"/>
+      <c r="C37" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="87"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="88"/>
-      <c r="H37" s="88"/>
-      <c r="I37" s="43" t="s">
+      <c r="D37" s="88"/>
+      <c r="E37" s="89"/>
+      <c r="F37" s="89"/>
+      <c r="G37" s="89"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="J37" s="44"/>
-      <c r="K37" s="62"/>
-      <c r="L37" s="62"/>
-      <c r="M37" s="62"/>
-      <c r="N37" s="62"/>
-      <c r="O37" s="62"/>
-      <c r="P37" s="62"/>
-      <c r="Q37" s="62"/>
-      <c r="R37" s="62"/>
-      <c r="S37" s="62"/>
-      <c r="T37" s="62"/>
-      <c r="U37" s="62"/>
-      <c r="V37" s="63" t="s">
+      <c r="J37" s="36"/>
+      <c r="K37" s="63"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="63"/>
+      <c r="O37" s="63"/>
+      <c r="P37" s="63"/>
+      <c r="Q37" s="63"/>
+      <c r="R37" s="63"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="63"/>
+      <c r="U37" s="63"/>
+      <c r="V37" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="W37" s="63"/>
-      <c r="X37" s="63"/>
-      <c r="Y37" s="64"/>
-      <c r="Z37" s="64"/>
-      <c r="AA37" s="64"/>
-      <c r="AB37" s="64"/>
-      <c r="AC37" s="64"/>
-      <c r="AD37" s="64"/>
-      <c r="AE37" s="64"/>
-      <c r="AF37" s="64"/>
+      <c r="W37" s="64"/>
+      <c r="X37" s="64"/>
+      <c r="Y37" s="65"/>
+      <c r="Z37" s="65"/>
+      <c r="AA37" s="65"/>
+      <c r="AB37" s="65"/>
+      <c r="AC37" s="65"/>
+      <c r="AD37" s="65"/>
+      <c r="AE37" s="65"/>
+      <c r="AF37" s="65"/>
       <c r="AG37" s="4"/>
       <c r="AH37" s="4"/>
       <c r="AI37" s="4"/>
       <c r="AJ37" s="4"/>
     </row>
     <row r="38" spans="1:36">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="43" t="s">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="89"/>
-      <c r="E38" s="89"/>
-      <c r="F38" s="89"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="92" t="s">
+      <c r="D38" s="90"/>
+      <c r="E38" s="90"/>
+      <c r="F38" s="90"/>
+      <c r="G38" s="90"/>
+      <c r="H38" s="90"/>
+      <c r="I38" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="J38" s="92"/>
-      <c r="K38" s="92"/>
-      <c r="L38" s="92"/>
-      <c r="M38" s="92"/>
-      <c r="N38" s="88"/>
-      <c r="O38" s="88"/>
-      <c r="P38" s="88"/>
-      <c r="Q38" s="88"/>
-      <c r="R38" s="88"/>
-      <c r="S38" s="88"/>
-      <c r="T38" s="88"/>
-      <c r="U38" s="88"/>
-      <c r="V38" s="88"/>
+      <c r="J38" s="93"/>
+      <c r="K38" s="93"/>
+      <c r="L38" s="93"/>
+      <c r="M38" s="93"/>
+      <c r="N38" s="89"/>
+      <c r="O38" s="89"/>
+      <c r="P38" s="89"/>
+      <c r="Q38" s="89"/>
+      <c r="R38" s="89"/>
+      <c r="S38" s="89"/>
+      <c r="T38" s="89"/>
+      <c r="U38" s="89"/>
+      <c r="V38" s="89"/>
       <c r="W38" s="93" t="s">
         <v>43</v>
       </c>
       <c r="X38" s="93"/>
       <c r="Y38" s="93"/>
       <c r="Z38" s="93"/>
-      <c r="AA38" s="64"/>
-      <c r="AB38" s="64"/>
-      <c r="AC38" s="64"/>
-      <c r="AD38" s="64"/>
-      <c r="AE38" s="64"/>
-      <c r="AF38" s="64"/>
+      <c r="AA38" s="65"/>
+      <c r="AB38" s="65"/>
+      <c r="AC38" s="65"/>
+      <c r="AD38" s="65"/>
+      <c r="AE38" s="65"/>
+      <c r="AF38" s="65"/>
       <c r="AG38" s="4"/>
       <c r="AH38" s="4"/>
       <c r="AI38" s="4"/>
       <c r="AJ38" s="4"/>
     </row>
     <row r="39" spans="1:36">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="43" t="s">
+      <c r="A39" s="19"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="91"/>
-      <c r="E39" s="91"/>
-      <c r="F39" s="91"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="91"/>
-      <c r="I39" s="91"/>
-      <c r="J39" s="91"/>
-      <c r="K39" s="91"/>
-      <c r="L39" s="91"/>
-      <c r="M39" s="91"/>
-      <c r="N39" s="91"/>
-      <c r="O39" s="91"/>
-      <c r="P39" s="91"/>
-      <c r="Q39" s="91"/>
-      <c r="R39" s="91"/>
-      <c r="S39" s="91"/>
-      <c r="T39" s="91"/>
-      <c r="U39" s="91"/>
-      <c r="V39" s="27"/>
-      <c r="W39" s="27"/>
-      <c r="X39" s="27"/>
-      <c r="Y39" s="27"/>
-      <c r="Z39" s="27"/>
-      <c r="AA39" s="27"/>
-      <c r="AB39" s="27"/>
-      <c r="AC39" s="27"/>
-      <c r="AD39" s="27"/>
-      <c r="AE39" s="27"/>
-      <c r="AF39" s="27"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="92"/>
+      <c r="I39" s="92"/>
+      <c r="J39" s="92"/>
+      <c r="K39" s="92"/>
+      <c r="L39" s="92"/>
+      <c r="M39" s="92"/>
+      <c r="N39" s="92"/>
+      <c r="O39" s="92"/>
+      <c r="P39" s="92"/>
+      <c r="Q39" s="92"/>
+      <c r="R39" s="92"/>
+      <c r="S39" s="92"/>
+      <c r="T39" s="92"/>
+      <c r="U39" s="92"/>
+      <c r="V39" s="19"/>
+      <c r="W39" s="19"/>
+      <c r="X39" s="19"/>
+      <c r="Y39" s="19"/>
+      <c r="Z39" s="19"/>
+      <c r="AA39" s="19"/>
+      <c r="AB39" s="19"/>
+      <c r="AC39" s="19"/>
+      <c r="AD39" s="19"/>
+      <c r="AE39" s="19"/>
+      <c r="AF39" s="19"/>
       <c r="AG39" s="4"/>
       <c r="AH39" s="4"/>
       <c r="AI39" s="4"/>
       <c r="AJ39" s="4"/>
     </row>
     <row r="40" spans="1:36" ht="6.75" customHeight="1">
-      <c r="A40" s="27"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="27"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-      <c r="W40" s="27"/>
-      <c r="X40" s="27"/>
-      <c r="Y40" s="27"/>
-      <c r="Z40" s="27"/>
-      <c r="AA40" s="27"/>
-      <c r="AB40" s="27"/>
-      <c r="AC40" s="27"/>
-      <c r="AD40" s="27"/>
-      <c r="AE40" s="27"/>
-      <c r="AF40" s="27"/>
+      <c r="A40" s="19"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="19"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="19"/>
+      <c r="U40" s="19"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="19"/>
+      <c r="X40" s="19"/>
+      <c r="Y40" s="19"/>
+      <c r="Z40" s="19"/>
+      <c r="AA40" s="19"/>
+      <c r="AB40" s="19"/>
+      <c r="AC40" s="19"/>
+      <c r="AD40" s="19"/>
+      <c r="AE40" s="19"/>
+      <c r="AF40" s="19"/>
       <c r="AG40" s="4"/>
       <c r="AH40" s="4"/>
       <c r="AI40" s="4"/>
       <c r="AJ40" s="4"/>
     </row>
     <row r="41" spans="1:36" ht="15.5">
-      <c r="A41" s="27"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="86" t="s">
+      <c r="A41" s="19"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="D41" s="86"/>
-      <c r="E41" s="86"/>
-      <c r="F41" s="86"/>
-      <c r="G41" s="86"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="90"/>
-      <c r="J41" s="90"/>
-      <c r="K41" s="90"/>
-      <c r="L41" s="90"/>
-      <c r="M41" s="90"/>
-      <c r="N41" s="90"/>
-      <c r="O41" s="90"/>
-      <c r="P41" s="90"/>
-      <c r="Q41" s="90"/>
-      <c r="R41" s="90"/>
-      <c r="S41" s="90"/>
-      <c r="T41" s="90"/>
-      <c r="U41" s="90"/>
-      <c r="V41" s="90"/>
-      <c r="W41" s="90"/>
-      <c r="X41" s="90"/>
-      <c r="Y41" s="90"/>
-      <c r="Z41" s="90"/>
-      <c r="AA41" s="90"/>
-      <c r="AB41" s="90"/>
-      <c r="AC41" s="90"/>
-      <c r="AD41" s="90"/>
-      <c r="AE41" s="90"/>
-      <c r="AF41" s="90"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="87"/>
+      <c r="F41" s="87"/>
+      <c r="G41" s="87"/>
+      <c r="H41" s="91"/>
+      <c r="I41" s="91"/>
+      <c r="J41" s="91"/>
+      <c r="K41" s="91"/>
+      <c r="L41" s="91"/>
+      <c r="M41" s="91"/>
+      <c r="N41" s="91"/>
+      <c r="O41" s="91"/>
+      <c r="P41" s="91"/>
+      <c r="Q41" s="91"/>
+      <c r="R41" s="91"/>
+      <c r="S41" s="91"/>
+      <c r="T41" s="91"/>
+      <c r="U41" s="91"/>
+      <c r="V41" s="91"/>
+      <c r="W41" s="91"/>
+      <c r="X41" s="91"/>
+      <c r="Y41" s="91"/>
+      <c r="Z41" s="91"/>
+      <c r="AA41" s="91"/>
+      <c r="AB41" s="91"/>
+      <c r="AC41" s="91"/>
+      <c r="AD41" s="91"/>
+      <c r="AE41" s="91"/>
+      <c r="AF41" s="91"/>
       <c r="AG41" s="4"/>
       <c r="AH41" s="4"/>
       <c r="AI41" s="4"/>
       <c r="AJ41" s="4"/>
     </row>
     <row r="42" spans="1:36" ht="16" customHeight="1">
-      <c r="A42" s="27"/>
+      <c r="A42" s="19"/>
       <c r="AG42" s="4"/>
       <c r="AH42" s="4"/>
       <c r="AI42" s="4"/>
       <c r="AJ42" s="4"/>
     </row>
     <row r="43" spans="1:36" ht="14.25" customHeight="1" thickBot="1">
-      <c r="G43" s="38"/>
+      <c r="G43" s="30"/>
       <c r="H43" s="57"/>
       <c r="I43" s="57"/>
       <c r="J43" s="57"/>
@@ -2777,7 +2782,7 @@
       <c r="M43" s="57"/>
       <c r="N43" s="57"/>
       <c r="O43" s="57"/>
-      <c r="P43" s="38"/>
+      <c r="P43" s="30"/>
       <c r="U43" s="57"/>
       <c r="V43" s="57"/>
       <c r="W43" s="57"/>
@@ -2808,10 +2813,10 @@
       <c r="O44" s="58"/>
       <c r="P44" s="58"/>
       <c r="Q44" s="58"/>
-      <c r="R44" s="39"/>
-      <c r="S44" s="23"/>
-      <c r="T44" s="23"/>
-      <c r="U44" s="23"/>
+      <c r="R44" s="31"/>
+      <c r="S44" s="15"/>
+      <c r="T44" s="15"/>
+      <c r="U44" s="15"/>
       <c r="V44" s="58" t="s">
         <v>47</v>
       </c>
@@ -2831,10 +2836,10 @@
       <c r="AJ44" s="4"/>
     </row>
     <row r="45" spans="1:36" ht="15" customHeight="1">
-      <c r="R45" s="40"/>
-      <c r="S45" s="40"/>
-      <c r="T45" s="40"/>
-      <c r="U45" s="40"/>
+      <c r="R45" s="32"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="32"/>
+      <c r="U45" s="32"/>
       <c r="V45" s="59"/>
       <c r="W45" s="59"/>
       <c r="X45" s="59"/>
@@ -2844,7 +2849,7 @@
       <c r="AB45" s="59"/>
       <c r="AC45" s="59"/>
       <c r="AD45" s="59"/>
-      <c r="AE45" s="41"/>
+      <c r="AE45" s="33"/>
       <c r="AG45" s="4"/>
       <c r="AH45" s="4"/>
       <c r="AI45" s="4"/>
